--- a/assets/templates/일일제거작업일지_표준템플릿.xlsx
+++ b/assets/templates/일일제거작업일지_표준템플릿.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="일일작업결과표_표준양식" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="예산사용현황" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -16,8 +17,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="4">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.0%"/>
+  </numFmts>
+  <fonts count="8">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -28,21 +31,45 @@
     <font>
       <name val="맑은 고딕"/>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="14"/>
+      <color rgb="001E293B"/>
+      <sz val="16"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <i val="1"/>
+      <color rgb="0064748B"/>
+      <sz val="10"/>
     </font>
     <font>
       <name val="맑은 고딕"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <color rgb="000F172A"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="맑은 고딕"/>
-      <sz val="9"/>
+      <b val="1"/>
+      <color rgb="001E3A8A"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <color rgb="0094A3B8"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <b val="1"/>
+      <color rgb="001E3A8A"/>
+      <sz val="10"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -57,8 +84,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="002563EB"/>
-        <bgColor rgb="002563EB"/>
+        <fgColor rgb="00F8FAFC"/>
+        <bgColor rgb="00F8FAFC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EFF6FF"/>
+        <bgColor rgb="00EFF6FF"/>
       </patternFill>
     </fill>
   </fills>
@@ -88,21 +121,59 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
@@ -470,304 +541,837 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P5"/>
+  <dimension ref="A1:P14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="24" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="6" max="6"/>
     <col width="9" customWidth="1" min="7" max="7"/>
-    <col width="10" customWidth="1" min="8" max="8"/>
-    <col width="11" customWidth="1" min="9" max="9"/>
-    <col width="11" customWidth="1" min="10" max="10"/>
-    <col width="11" customWidth="1" min="11" max="11"/>
-    <col width="14" customWidth="1" min="12" max="12"/>
-    <col width="15" customWidth="1" min="13" max="13"/>
+    <col width="8" customWidth="1" min="8" max="8"/>
+    <col width="8" customWidth="1" min="9" max="9"/>
+    <col width="8" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="10" customWidth="1" min="12" max="12"/>
+    <col width="16" customWidth="1" min="13" max="13"/>
     <col width="10" customWidth="1" min="14" max="14"/>
-    <col width="10" customWidth="1" min="15" max="15"/>
-    <col width="32" customWidth="1" min="16" max="16"/>
+    <col width="18" customWidth="1" min="15" max="15"/>
+    <col width="30" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
-    <row r="1" ht="35" customHeight="1">
+    <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>생태계교란생물 / 외래생물 제거사업 일일 작업결과표 (표준양식)</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="32" customHeight="1">
+          <t>2026년 생태계교란생물 / 외래생물 제거사업 일일 작업결과표 (공통 표준양식)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>회차
-(No)</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
+          <t>※ (사)야생생물관리협회 전국 지부 및 유역환경청 보고용 공통 표준 서식 (구간 구분 없이 사업 대상지 전체 단위로 작성)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="24" customHeight="1">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>구분
+(회차)</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>대상식물 / 생물
+(종명)</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>작업장소
+(대상지 일원)</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
         <is>
           <t>작업일자
 (YYYY-MM-DD)</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>작업구간
-(구간명)</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>대상생물
-(종명)</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>작업장소
-(세부지명)</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>제거/포획방법</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t>로제트</t>
-        </is>
-      </c>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>영양생장</t>
-        </is>
-      </c>
-      <c r="I2" s="2" t="inlineStr">
-        <is>
-          <t>개화/성체</t>
-        </is>
-      </c>
-      <c r="J2" s="2" t="inlineStr">
-        <is>
-          <t>결실/유생</t>
-        </is>
-      </c>
-      <c r="K2" s="2" t="inlineStr">
-        <is>
-          <t>고사/난괴</t>
-        </is>
-      </c>
-      <c r="L2" s="2" t="inlineStr">
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>제거 / 포획방법</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>생육단계 (해당란 √ 표시)</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="n"/>
+      <c r="H4" s="4" t="n"/>
+      <c r="I4" s="4" t="n"/>
+      <c r="J4" s="4" t="n"/>
+      <c r="K4" s="3" t="inlineStr">
         <is>
           <t>제거면적
 (㎡)</t>
         </is>
       </c>
-      <c r="M2" s="2" t="inlineStr">
-        <is>
-          <t>제거량/포획량
-(kg / 마리)</t>
-        </is>
-      </c>
-      <c r="N2" s="2" t="inlineStr">
+      <c r="L4" s="3" t="inlineStr">
+        <is>
+          <t>소요시간
+(시간)</t>
+        </is>
+      </c>
+      <c r="M4" s="3" t="inlineStr">
+        <is>
+          <t>제거량 / 포획량
+(kg 또는 마리)</t>
+        </is>
+      </c>
+      <c r="N4" s="3" t="inlineStr">
         <is>
           <t>투입인력
 (명)</t>
         </is>
       </c>
-      <c r="O2" s="2" t="inlineStr">
-        <is>
-          <t>소요시간
-(시간)</t>
-        </is>
-      </c>
-      <c r="P2" s="2" t="inlineStr">
-        <is>
-          <t>작업세부 및 현장 특이사항</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="22" customHeight="1">
-      <c r="A3" s="3" t="n">
+      <c r="O4" s="3" t="inlineStr">
+        <is>
+          <t>제거종
+(상세)</t>
+        </is>
+      </c>
+      <c r="P4" s="3" t="inlineStr">
+        <is>
+          <t>비고 / 작업세부사항
+(특이사항)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="22" customHeight="1">
+      <c r="A5" s="4" t="n"/>
+      <c r="B5" s="4" t="n"/>
+      <c r="C5" s="4" t="n"/>
+      <c r="D5" s="4" t="n"/>
+      <c r="E5" s="4" t="n"/>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>로제트</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>영양생장</t>
+        </is>
+      </c>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>개화</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t>결실</t>
+        </is>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>고사</t>
+        </is>
+      </c>
+      <c r="K5" s="4" t="n"/>
+      <c r="L5" s="4" t="n"/>
+      <c r="M5" s="4" t="n"/>
+      <c r="N5" s="4" t="n"/>
+      <c r="O5" s="4" t="n"/>
+      <c r="P5" s="4" t="n"/>
+    </row>
+    <row r="6" ht="22" customHeight="1">
+      <c r="A6" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>가시박, 환삼덩굴</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>천내리 습지 일대</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="E6" s="6" t="inlineStr">
+        <is>
+          <t>손으로 뿌리뽑기</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="G6" s="5" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr"/>
+      <c r="I6" s="7" t="inlineStr"/>
+      <c r="J6" s="7" t="inlineStr"/>
+      <c r="K6" s="8" t="n">
+        <v>18000</v>
+      </c>
+      <c r="L6" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="M6" s="8" t="n">
+        <v>80</v>
+      </c>
+      <c r="N6" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="O6" s="6" t="inlineStr">
+        <is>
+          <t>가시박, 환삼덩굴</t>
+        </is>
+      </c>
+      <c r="P6" s="6" t="inlineStr">
+        <is>
+          <t>발아기 유묘 및 로제트 손 뿌리뽑기 집중</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="22" customHeight="1">
+      <c r="A7" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>가시박, 환삼덩굴</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>천내리 습지 일대</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="E7" s="6" t="inlineStr">
+        <is>
+          <t>낫으로 베기, 예초기 사용</t>
+        </is>
+      </c>
+      <c r="F7" s="7" t="inlineStr"/>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="H7" s="7" t="inlineStr"/>
+      <c r="I7" s="7" t="inlineStr"/>
+      <c r="J7" s="7" t="inlineStr"/>
+      <c r="K7" s="8" t="n">
+        <v>48000</v>
+      </c>
+      <c r="L7" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="M7" s="8" t="n">
+        <v>800</v>
+      </c>
+      <c r="N7" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="O7" s="6" t="inlineStr">
+        <is>
+          <t>가시박, 환삼덩굴</t>
+        </is>
+      </c>
+      <c r="P7" s="6" t="inlineStr">
+        <is>
+          <t>영양생장기 대군락지 예초 및 지상부 낫베기</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="22" customHeight="1">
+      <c r="A8" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>황소개구리, 미국수련</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>두웅습지 일원</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
         <is>
           <t>2026-08-20</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
-        <is>
-          <t>1구간</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>미국수련, 마름</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>두웅습지 개방수면부</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>수거망·지하경 굴취</t>
-        </is>
-      </c>
-      <c r="G3" s="3" t="inlineStr"/>
-      <c r="H3" s="3" t="inlineStr">
+      <c r="E8" s="6" t="inlineStr">
+        <is>
+          <t>포획통발 가동, 뿌리 굴취</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr"/>
+      <c r="G8" s="5" t="inlineStr">
         <is>
           <t>√</t>
         </is>
       </c>
-      <c r="I3" s="3" t="inlineStr">
+      <c r="H8" s="5" t="inlineStr">
         <is>
           <t>√</t>
         </is>
       </c>
-      <c r="J3" s="3" t="inlineStr"/>
-      <c r="K3" s="3" t="inlineStr"/>
-      <c r="L3" s="5" t="n">
+      <c r="I8" s="7" t="inlineStr"/>
+      <c r="J8" s="7" t="inlineStr"/>
+      <c r="K8" s="8" t="n">
         <v>1200</v>
       </c>
-      <c r="M3" s="5" t="n">
+      <c r="L8" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="M8" s="8" t="n">
         <v>350</v>
       </c>
-      <c r="N3" s="3" t="n">
+      <c r="N8" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="O3" s="3" t="n">
+      <c r="O8" s="6" t="inlineStr">
+        <is>
+          <t>미국수련, 황소개구리</t>
+        </is>
+      </c>
+      <c r="P8" s="6" t="inlineStr">
+        <is>
+          <t>수생식물 지하경 굴취 및 황소개구리 포획통발 15개소 가동</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="22" customHeight="1">
+      <c r="A9" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="B9" s="9" t="inlineStr"/>
+      <c r="C9" s="9" t="inlineStr"/>
+      <c r="D9" s="7" t="inlineStr"/>
+      <c r="E9" s="9" t="inlineStr"/>
+      <c r="F9" s="7" t="inlineStr"/>
+      <c r="G9" s="7" t="inlineStr"/>
+      <c r="H9" s="7" t="inlineStr"/>
+      <c r="I9" s="7" t="inlineStr"/>
+      <c r="J9" s="7" t="inlineStr"/>
+      <c r="K9" s="10" t="inlineStr"/>
+      <c r="L9" s="10" t="inlineStr"/>
+      <c r="M9" s="10" t="inlineStr"/>
+      <c r="N9" s="10" t="inlineStr"/>
+      <c r="O9" s="9" t="inlineStr"/>
+      <c r="P9" s="9" t="inlineStr"/>
+    </row>
+    <row r="10" ht="22" customHeight="1">
+      <c r="A10" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="B10" s="9" t="inlineStr"/>
+      <c r="C10" s="9" t="inlineStr"/>
+      <c r="D10" s="7" t="inlineStr"/>
+      <c r="E10" s="9" t="inlineStr"/>
+      <c r="F10" s="7" t="inlineStr"/>
+      <c r="G10" s="7" t="inlineStr"/>
+      <c r="H10" s="7" t="inlineStr"/>
+      <c r="I10" s="7" t="inlineStr"/>
+      <c r="J10" s="7" t="inlineStr"/>
+      <c r="K10" s="10" t="inlineStr"/>
+      <c r="L10" s="10" t="inlineStr"/>
+      <c r="M10" s="10" t="inlineStr"/>
+      <c r="N10" s="10" t="inlineStr"/>
+      <c r="O10" s="9" t="inlineStr"/>
+      <c r="P10" s="9" t="inlineStr"/>
+    </row>
+    <row r="11" ht="22" customHeight="1">
+      <c r="A11" s="7" t="n">
         <v>6</v>
       </c>
-      <c r="P3" s="4" t="inlineStr">
-        <is>
-          <t>지하경 중심 집중 굴취 및 육상 반출</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="22" customHeight="1">
-      <c r="A4" s="3" t="n">
-        <v>2</v>
+      <c r="B11" s="9" t="inlineStr"/>
+      <c r="C11" s="9" t="inlineStr"/>
+      <c r="D11" s="7" t="inlineStr"/>
+      <c r="E11" s="9" t="inlineStr"/>
+      <c r="F11" s="7" t="inlineStr"/>
+      <c r="G11" s="7" t="inlineStr"/>
+      <c r="H11" s="7" t="inlineStr"/>
+      <c r="I11" s="7" t="inlineStr"/>
+      <c r="J11" s="7" t="inlineStr"/>
+      <c r="K11" s="10" t="inlineStr"/>
+      <c r="L11" s="10" t="inlineStr"/>
+      <c r="M11" s="10" t="inlineStr"/>
+      <c r="N11" s="10" t="inlineStr"/>
+      <c r="O11" s="9" t="inlineStr"/>
+      <c r="P11" s="9" t="inlineStr"/>
+    </row>
+    <row r="12" ht="22" customHeight="1">
+      <c r="A12" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="B12" s="9" t="inlineStr"/>
+      <c r="C12" s="9" t="inlineStr"/>
+      <c r="D12" s="7" t="inlineStr"/>
+      <c r="E12" s="9" t="inlineStr"/>
+      <c r="F12" s="7" t="inlineStr"/>
+      <c r="G12" s="7" t="inlineStr"/>
+      <c r="H12" s="7" t="inlineStr"/>
+      <c r="I12" s="7" t="inlineStr"/>
+      <c r="J12" s="7" t="inlineStr"/>
+      <c r="K12" s="10" t="inlineStr"/>
+      <c r="L12" s="10" t="inlineStr"/>
+      <c r="M12" s="10" t="inlineStr"/>
+      <c r="N12" s="10" t="inlineStr"/>
+      <c r="O12" s="9" t="inlineStr"/>
+      <c r="P12" s="9" t="inlineStr"/>
+    </row>
+    <row r="13" ht="22" customHeight="1">
+      <c r="A13" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="B13" s="9" t="inlineStr"/>
+      <c r="C13" s="9" t="inlineStr"/>
+      <c r="D13" s="7" t="inlineStr"/>
+      <c r="E13" s="9" t="inlineStr"/>
+      <c r="F13" s="7" t="inlineStr"/>
+      <c r="G13" s="7" t="inlineStr"/>
+      <c r="H13" s="7" t="inlineStr"/>
+      <c r="I13" s="7" t="inlineStr"/>
+      <c r="J13" s="7" t="inlineStr"/>
+      <c r="K13" s="10" t="inlineStr"/>
+      <c r="L13" s="10" t="inlineStr"/>
+      <c r="M13" s="10" t="inlineStr"/>
+      <c r="N13" s="10" t="inlineStr"/>
+      <c r="O13" s="9" t="inlineStr"/>
+      <c r="P13" s="9" t="inlineStr"/>
+    </row>
+    <row r="14" ht="24" customHeight="1">
+      <c r="A14" s="11" t="inlineStr">
+        <is>
+          <t>누적 합계 (SUM)</t>
+        </is>
+      </c>
+      <c r="B14" s="12" t="n"/>
+      <c r="C14" s="12" t="n"/>
+      <c r="D14" s="12" t="n"/>
+      <c r="E14" s="12" t="n"/>
+      <c r="F14" s="13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G14" s="13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H14" s="13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I14" s="13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J14" s="13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K14" s="14">
+        <f>SUM(K6:K13)</f>
+        <v/>
+      </c>
+      <c r="L14" s="14">
+        <f>SUM(L6:L13)</f>
+        <v/>
+      </c>
+      <c r="M14" s="14">
+        <f>SUM(M6:M13)</f>
+        <v/>
+      </c>
+      <c r="N14" s="14">
+        <f>SUM(N6:N13)</f>
+        <v/>
+      </c>
+      <c r="O14" s="12" t="inlineStr"/>
+      <c r="P14" s="12" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <mergeCells count="15">
+    <mergeCell ref="M4:M5"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="C4:C5"/>
+    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="D4:D5"/>
+    <mergeCell ref="A2:N2"/>
+    <mergeCell ref="E4:E5"/>
+    <mergeCell ref="N4:N5"/>
+    <mergeCell ref="K4:K5"/>
+    <mergeCell ref="L4:L5"/>
+    <mergeCell ref="O4:O5"/>
+    <mergeCell ref="P4:P5"/>
+    <mergeCell ref="A14:E14"/>
+    <mergeCell ref="F4:J4"/>
+    <mergeCell ref="A1:N1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>생태계교란생물 제거사업 예산 사용 및 집행 현황</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="18" customHeight="1">
+      <c r="A2" s="15" t="inlineStr">
+        <is>
+          <t>(단위: 원, 부가세 포함 기준)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="24" customHeight="1">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>구분</t>
+        </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>예산 세부항목</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>2구간</t>
-        </is>
-      </c>
-      <c r="D4" s="4" t="inlineStr">
-        <is>
-          <t>황소개구리</t>
-        </is>
-      </c>
-      <c r="E4" s="4" t="inlineStr">
-        <is>
-          <t>수변부 갈대군락</t>
-        </is>
-      </c>
-      <c r="F4" s="4" t="inlineStr">
-        <is>
-          <t>포획통발·뜰채</t>
-        </is>
-      </c>
-      <c r="G4" s="3" t="inlineStr"/>
-      <c r="H4" s="3" t="inlineStr"/>
-      <c r="I4" s="3" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="J4" s="3" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="K4" s="3" t="inlineStr"/>
-      <c r="L4" s="5" t="n">
-        <v>2500</v>
-      </c>
-      <c r="M4" s="5" t="n">
-        <v>85</v>
-      </c>
-      <c r="N4" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="O4" s="3" t="n">
-        <v>6</v>
-      </c>
-      <c r="P4" s="4" t="inlineStr">
-        <is>
-          <t>포획통발 15개소 설치 및 성체 42마리 포획</t>
+          <t>예산액 (원)</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>집행액 (원)</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>잔액 (원)</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>집행률 (%)</t>
         </is>
       </c>
     </row>
     <row r="5" ht="22" customHeight="1">
-      <c r="A5" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t>1구간</t>
-        </is>
-      </c>
-      <c r="D5" s="4" t="inlineStr">
-        <is>
-          <t>미국수련</t>
-        </is>
-      </c>
-      <c r="E5" s="4" t="inlineStr">
-        <is>
-          <t>목재데크 관찰로 주변</t>
-        </is>
-      </c>
-      <c r="F5" s="4" t="inlineStr">
-        <is>
-          <t>수거망 사용</t>
-        </is>
-      </c>
-      <c r="G5" s="3" t="inlineStr"/>
-      <c r="H5" s="3" t="inlineStr">
-        <is>
-          <t>√</t>
-        </is>
-      </c>
-      <c r="I5" s="3" t="inlineStr"/>
-      <c r="J5" s="3" t="inlineStr"/>
-      <c r="K5" s="3" t="inlineStr"/>
-      <c r="L5" s="5" t="n">
-        <v>800</v>
-      </c>
-      <c r="M5" s="5" t="n">
-        <v>200</v>
-      </c>
-      <c r="N5" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="O5" s="3" t="n">
-        <v>6</v>
-      </c>
-      <c r="P5" s="4" t="inlineStr">
-        <is>
-          <t>2차 신규 발아 개체 반복 수거</t>
-        </is>
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>인건비</t>
+        </is>
+      </c>
+      <c r="B5" s="9" t="inlineStr">
+        <is>
+          <t>특별인부 (작업원 인건비)</t>
+        </is>
+      </c>
+      <c r="C5" s="16" t="n">
+        <v>10175490</v>
+      </c>
+      <c r="D5" s="16">
+        <f> 일일작업결과표_표준양식!N14 * 226122</f>
+        <v/>
+      </c>
+      <c r="E5" s="16">
+        <f>C5-D5</f>
+        <v/>
+      </c>
+      <c r="F5" s="17">
+        <f>D5/C5</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6" ht="22" customHeight="1">
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t>인건비</t>
+        </is>
+      </c>
+      <c r="B6" s="9" t="inlineStr">
+        <is>
+          <t>관리자 인건비 (연구보조원 등)</t>
+        </is>
+      </c>
+      <c r="C6" s="16" t="n">
+        <v>1993000</v>
+      </c>
+      <c r="D6" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" s="16">
+        <f>C6-D6</f>
+        <v/>
+      </c>
+      <c r="F6" s="17">
+        <f>D6/C6</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7" ht="22" customHeight="1">
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t>경비</t>
+        </is>
+      </c>
+      <c r="B7" s="9" t="inlineStr">
+        <is>
+          <t>조사단 운영비 (책임/전문조사원)</t>
+        </is>
+      </c>
+      <c r="C7" s="16" t="n">
+        <v>615124</v>
+      </c>
+      <c r="D7" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" s="16">
+        <f>C7-D7</f>
+        <v/>
+      </c>
+      <c r="F7" s="17">
+        <f>D7/C7</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8" ht="22" customHeight="1">
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t>경비</t>
+        </is>
+      </c>
+      <c r="B8" s="9" t="inlineStr">
+        <is>
+          <t>회의비 및 사전 안전교육비</t>
+        </is>
+      </c>
+      <c r="C8" s="16" t="n">
+        <v>200000</v>
+      </c>
+      <c r="D8" s="16" t="n">
+        <v>100000</v>
+      </c>
+      <c r="E8" s="16">
+        <f>C8-D8</f>
+        <v/>
+      </c>
+      <c r="F8" s="17">
+        <f>D8/C8</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9" ht="22" customHeight="1">
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t>경비</t>
+        </is>
+      </c>
+      <c r="B9" s="9" t="inlineStr">
+        <is>
+          <t>재료비 (예초기 날, 소모품 등)</t>
+        </is>
+      </c>
+      <c r="C9" s="16" t="n">
+        <v>450000</v>
+      </c>
+      <c r="D9" s="16" t="n">
+        <v>260000</v>
+      </c>
+      <c r="E9" s="16">
+        <f>C9-D9</f>
+        <v/>
+      </c>
+      <c r="F9" s="17">
+        <f>D9/C9</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="22" customHeight="1">
+      <c r="A10" s="7" t="inlineStr">
+        <is>
+          <t>경비</t>
+        </is>
+      </c>
+      <c r="B10" s="9" t="inlineStr">
+        <is>
+          <t>홍보비 (현수막 제작 등)</t>
+        </is>
+      </c>
+      <c r="C10" s="16" t="n">
+        <v>30000</v>
+      </c>
+      <c r="D10" s="16" t="n">
+        <v>30000</v>
+      </c>
+      <c r="E10" s="16">
+        <f>C10-D10</f>
+        <v/>
+      </c>
+      <c r="F10" s="17">
+        <f>D10/C10</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" ht="22" customHeight="1">
+      <c r="A11" s="7" t="inlineStr">
+        <is>
+          <t>경비</t>
+        </is>
+      </c>
+      <c r="B11" s="9" t="inlineStr">
+        <is>
+          <t>결과보고서 제작 및 인쇄비</t>
+        </is>
+      </c>
+      <c r="C11" s="16" t="n">
+        <v>250000</v>
+      </c>
+      <c r="D11" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" s="16">
+        <f>C11-D11</f>
+        <v/>
+      </c>
+      <c r="F11" s="17">
+        <f>D11/C11</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12" ht="22" customHeight="1">
+      <c r="A12" s="7" t="inlineStr">
+        <is>
+          <t>경비</t>
+        </is>
+      </c>
+      <c r="B12" s="9" t="inlineStr">
+        <is>
+          <t>안전보건관리비 (상해보험료 등)</t>
+        </is>
+      </c>
+      <c r="C12" s="16" t="n">
+        <v>455000</v>
+      </c>
+      <c r="D12" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" s="16">
+        <f>C12-D12</f>
+        <v/>
+      </c>
+      <c r="F12" s="17">
+        <f>D12/C12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" ht="22" customHeight="1">
+      <c r="A13" s="7" t="inlineStr">
+        <is>
+          <t>일반관리비</t>
+        </is>
+      </c>
+      <c r="B13" s="9" t="inlineStr">
+        <is>
+          <t>일반관리비</t>
+        </is>
+      </c>
+      <c r="C13" s="16" t="n">
+        <v>831600</v>
+      </c>
+      <c r="D13" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" s="16">
+        <f>C13-D13</f>
+        <v/>
+      </c>
+      <c r="F13" s="17">
+        <f>D13/C13</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14" ht="24" customHeight="1">
+      <c r="A14" s="11" t="inlineStr">
+        <is>
+          <t>총 계</t>
+        </is>
+      </c>
+      <c r="B14" s="18" t="inlineStr">
+        <is>
+          <t>사업비 총괄 합계</t>
+        </is>
+      </c>
+      <c r="C14" s="14">
+        <f>SUM(C5:C13)</f>
+        <v/>
+      </c>
+      <c r="D14" s="14">
+        <f>SUM(D5:D13)</f>
+        <v/>
+      </c>
+      <c r="E14" s="14">
+        <f>SUM(E5:E13)</f>
+        <v/>
+      </c>
+      <c r="F14" s="19">
+        <f>D14/C14</f>
+        <v/>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:P1"/>
+  <mergeCells count="2">
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A1:F1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
